--- a/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:59</t>
+          <t>2026-10-14 01:01:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:59</t>
+          <t>2026-10-14 01:01:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:59</t>
+          <t>2026-10-14 01:01:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:01</t>
+          <t>2026-10-14 01:01:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:02</t>
+          <t>2026-10-14 01:01:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:08</t>
+          <t>2026-10-14 21:55:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,40 +504,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.27%633,000</t>
+          <t>2.77%406,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>633000</v>
+        <v>406000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:08</t>
+          <t>2026-10-14 21:55:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,40 +567,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6857ADVANTEST CORP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.80%406,000</t>
+          <t>2.32%103,200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>406000</v>
+        <v>103200</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:08</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,44 +626,44 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.35%103,200</t>
+          <t>2.16%667,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>103200</v>
+        <v>667000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,40 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.27%667,000</t>
+          <t>2.05%165,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>667000</v>
+        <v>165000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.24%134,000</t>
+          <t>2.04%420,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>134000</v>
+        <v>420000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -819,40 +819,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.07%165,000</t>
+          <t>2.04%134,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>165000</v>
+        <v>134000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>6920LASERTEC CORP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -902,16 +902,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.82%418,400</t>
+          <t>1.59%62,100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>418400</v>
+        <v>62100</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,40 +945,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6920LASERTEC CORP</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.65%62,100</t>
+          <t>1.42%158,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>62100</v>
+        <v>158000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.49%236,200</t>
+          <t>1.40%236,200</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:09</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1067,44 +1067,44 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.45%158,000</t>
+          <t>1.37%348,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>158000</v>
+        <v>348000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,40 +1134,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.36%348,000</t>
+          <t>1.08%193,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>348000</v>
+        <v>193000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1197,40 +1197,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>-2.79%296.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>296.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.12%193,000</t>
+          <t>0.81%967,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>193000</v>
+        <v>967000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,27 +1265,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.83%130,000</t>
+          <t>0.78%130,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1323,40 +1323,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.67%305</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.79%967,000</t>
+          <t>0.74%174,300</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>967000</v>
+        <v>174300</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,27 +1391,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.99%552</t>
+          <t>+2.72%567</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.57%364,000</t>
+          <t>0.55%364,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1449,40 +1449,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.52%156,000</t>
+          <t>0.51%23,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>156000</v>
+        <v>23000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:11</t>
+          <t>2026-10-14 21:56:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1512,40 +1512,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>0.50%156,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>23000</v>
+        <v>156000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">

--- a/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:55:58</t>
+          <t>2026-10-14 22:01:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:55:58</t>
+          <t>2026-10-14 22:01:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:10</t>
+          <t>2026-10-14 22:01:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:21</t>
+          <t>2026-10-14 22:02:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:58</t>
+          <t>2026-10-14 22:32:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:58</t>
+          <t>2026-10-14 22:32:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:59</t>
+          <t>2026-10-14 22:32:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:00</t>
+          <t>2026-10-14 22:32:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
